--- a/data/export/2026-10-20-operations.xlsx
+++ b/data/export/2026-10-20-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -442,7 +442,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,33 +704,37 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -759,32 +767,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -792,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,17 +828,17 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -836,13 +848,17 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -875,32 +891,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:39</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -908,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -932,33 +952,37 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1048,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1063,7 +1087,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1074,7 +1098,7 @@
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1107,32 +1131,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1140,7 +1168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1164,17 +1192,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1184,13 +1212,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1288,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1338,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1404,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1454,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1467,22 @@
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>沪A35717D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1483,12 +1515,12 @@
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1502,7 +1534,7 @@
       <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1538,35 +1570,35 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1599,12 +1631,12 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1618,7 +1650,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1654,35 +1686,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1747,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1766,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1802,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1831,12 +1863,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1882,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1886,35 +1918,35 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1979,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +1998,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,46 +2023,50 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2099,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2118,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2118,35 +2154,35 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2215,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2234,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2270,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2331,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2350,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,46 +2375,50 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2411,12 +2451,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2470,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2455,7 +2495,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2466,25 +2506,25 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2494,7 +2534,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2532,7 +2572,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2582,35 +2622,35 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2648,7 +2688,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2662,7 +2702,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2698,35 +2738,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2764,7 +2804,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2778,7 +2818,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2814,35 +2854,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2875,12 +2915,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2894,7 +2934,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2930,7 +2970,3719 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>沪A72305D</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-operations.xlsx
+++ b/data/export/2026-10-20-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD53"/>
+  <dimension ref="A1:AD81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -450,7 +450,7 @@
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,14 +843,14 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>75.0</t>
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -901,12 +901,12 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1015,32 +1015,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1048,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1072,17 +1076,17 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1092,13 +1096,17 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1207,14 +1215,14 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
           <t>83.0</t>
@@ -1222,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1263,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -1288,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1312,33 +1324,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1371,32 +1387,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1404,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1428,33 +1448,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1511,36 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:32</t>
@@ -1520,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1544,33 +1572,37 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1675,7 +1707,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1686,7 +1718,7 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1719,32 +1751,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1752,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1776,33 +1812,37 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1908,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1918,7 +1958,7 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1984,7 +2024,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2038,7 +2078,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2144,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2154,7 +2194,7 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2260,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2270,7 +2310,7 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2376,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2385,12 +2425,12 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2403,22 +2443,22 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2456,7 +2496,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2470,7 +2510,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2500,41 +2540,45 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2567,12 +2611,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2586,7 +2630,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2611,46 +2655,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2683,12 +2731,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2702,7 +2750,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2727,46 +2775,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2799,12 +2851,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2818,7 +2870,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2854,35 +2906,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2915,12 +2967,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2934,7 +2986,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2959,46 +3011,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3031,12 +3087,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3050,7 +3106,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3075,46 +3131,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3147,12 +3207,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3166,7 +3226,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3191,46 +3251,50 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3263,12 +3327,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3282,7 +3346,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3307,46 +3371,50 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3379,12 +3447,12 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3398,7 +3466,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3423,7 +3491,7 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
@@ -3434,7 +3502,7 @@
       <c r="AC25" s="2" t="inlineStr"/>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3515,7 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3457,7 +3525,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3467,40 +3535,44 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3514,7 +3586,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3524,33 +3596,37 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3639,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3573,7 +3649,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3583,40 +3659,44 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3630,7 +3710,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3640,33 +3720,37 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3679,60 +3763,64 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3746,7 +3834,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3756,17 +3844,17 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3776,13 +3864,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3887,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3805,7 +3897,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3815,40 +3907,44 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3862,7 +3958,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3872,33 +3968,37 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3911,7 +4011,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3921,7 +4021,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3931,12 +4031,12 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq36，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3959,12 +4059,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3972,13 +4072,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="2" t="inlineStr"/>
-      <c r="T30" s="2" t="inlineStr"/>
-      <c r="U30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 12分钟参与校验</t>
+        </is>
+      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4014,7 +4130,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4027,22 +4143,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4075,12 +4191,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4094,7 +4210,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4130,7 +4246,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4259,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4153,7 +4269,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4191,12 +4307,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4210,7 +4326,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4246,7 +4362,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4375,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4269,7 +4385,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4307,12 +4423,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4326,7 +4442,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4362,7 +4478,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4375,7 +4491,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4385,7 +4501,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4423,12 +4539,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4442,7 +4558,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4478,7 +4594,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4607,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4501,7 +4617,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4539,12 +4655,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4558,7 +4674,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4594,7 +4710,7 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4723,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4617,7 +4733,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4655,12 +4771,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4674,7 +4790,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4710,7 +4826,7 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4723,22 +4839,22 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4771,12 +4887,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4790,7 +4906,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4826,35 +4942,35 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4887,12 +5003,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4906,7 +5022,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4931,7 +5047,7 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -4942,35 +5058,35 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5003,12 +5119,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5022,7 +5138,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5058,35 +5174,35 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5119,12 +5235,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5138,7 +5254,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5174,35 +5290,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5235,12 +5351,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5254,7 +5370,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5290,35 +5406,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5351,12 +5467,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5370,7 +5486,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5406,35 +5522,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5467,12 +5583,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5486,7 +5602,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5522,35 +5638,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5583,12 +5699,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5602,7 +5718,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5638,35 +5754,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5699,12 +5815,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5718,7 +5834,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5754,35 +5870,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5815,12 +5931,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5834,7 +5950,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5870,35 +5986,35 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5931,12 +6047,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5950,7 +6066,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5986,35 +6102,35 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6047,12 +6163,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6066,7 +6182,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6102,35 +6218,35 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6163,12 +6279,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6182,7 +6298,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6218,35 +6334,35 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6279,12 +6395,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6298,7 +6414,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6334,35 +6450,35 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6395,12 +6511,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6414,7 +6530,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6450,35 +6566,35 @@
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6516,7 +6632,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6530,7 +6646,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6566,35 +6682,35 @@
       <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6627,12 +6743,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6646,7 +6762,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6671,7 +6787,7 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
@@ -6682,7 +6798,3315 @@
       <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>104分钟</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>101分钟</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-20-operations.xlsx
+++ b/data/export/2026-10-20-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD81"/>
+  <dimension ref="A1:AD98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -447,7 +447,7 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
     <col width="36" customWidth="1" min="21" max="21"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -719,22 +719,22 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1635,32 +1635,36 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -1668,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1692,17 +1696,17 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1712,13 +1716,17 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1761,24 +1769,24 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>102分钟</t>
+          <t>108分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1788,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1837,12 +1845,12 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1875,32 +1883,36 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1908,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1932,33 +1944,37 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1991,32 +2007,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2024,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2048,37 +2068,37 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2111,32 +2131,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -2144,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2168,33 +2192,37 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2288,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2376,7 +2404,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2415,7 +2443,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2430,7 +2458,7 @@
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2524,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2550,7 +2578,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2644,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2736,7 +2764,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2856,7 +2884,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2972,7 +3000,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3026,7 +3054,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3120,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3212,7 +3240,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3266,7 +3294,7 @@
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3360,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3381,12 +3409,12 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3480,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3496,83 +3524,83 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3586,7 +3614,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3596,17 +3624,17 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3621,82 +3649,78 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3710,7 +3734,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3720,107 +3744,103 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3834,7 +3854,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3844,107 +3864,103 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3958,7 +3974,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3968,22 +3984,22 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -3993,12 +4009,12 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4011,32 +4027,32 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>06:36</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq36，推进8站，达到≥2站确认条件</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4064,7 +4080,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4072,29 +4088,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>丁香路锦绣路</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>07:41</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>07:50</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 12分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4163,40 +4163,44 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4210,7 +4214,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4220,33 +4224,37 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4259,52 +4267,56 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4312,7 +4324,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4326,7 +4338,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4336,33 +4348,37 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4375,60 +4391,64 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4442,7 +4462,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4452,33 +4472,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4491,32 +4515,32 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq56，推进28站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -4539,12 +4563,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4552,13 +4576,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R34" s="2" t="inlineStr"/>
-      <c r="S34" s="2" t="inlineStr"/>
-      <c r="T34" s="2" t="inlineStr"/>
-      <c r="U34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 12分钟参与校验</t>
+        </is>
+      </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4583,7 +4623,7 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
@@ -4607,7 +4647,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4617,7 +4657,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4627,40 +4667,44 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4674,7 +4718,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4684,33 +4728,37 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4771,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4733,7 +4781,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4743,40 +4791,44 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4790,7 +4842,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4800,33 +4852,37 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4839,60 +4895,64 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4906,7 +4966,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4916,33 +4976,37 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4955,22 +5019,22 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -5003,12 +5067,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5022,7 +5086,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5071,22 +5135,22 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5119,12 +5183,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5138,7 +5202,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5163,7 +5227,7 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
@@ -5187,7 +5251,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5197,7 +5261,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5235,12 +5299,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5254,7 +5318,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5303,32 +5367,32 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq41推进至seq44，推进3站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -5351,12 +5415,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5364,13 +5428,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R41" s="2" t="inlineStr"/>
-      <c r="S41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
       <c r="T41" s="2" t="inlineStr"/>
-      <c r="U41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq23映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5419,22 +5495,22 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5467,12 +5543,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5486,7 +5562,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5535,22 +5611,22 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5583,12 +5659,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5602,7 +5678,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5651,7 +5727,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5661,7 +5737,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5699,12 +5775,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5718,7 +5794,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5767,7 +5843,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5777,7 +5853,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5815,12 +5891,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5834,7 +5910,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5883,7 +5959,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5893,7 +5969,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5931,12 +6007,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5950,7 +6026,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5999,7 +6075,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -6009,7 +6085,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -6047,12 +6123,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6066,7 +6142,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6115,7 +6191,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6125,7 +6201,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6163,12 +6239,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6182,7 +6258,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6231,7 +6307,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6241,7 +6317,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6279,12 +6355,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6298,7 +6374,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6347,7 +6423,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6357,7 +6433,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6395,12 +6471,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6414,7 +6490,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6463,22 +6539,22 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6511,12 +6587,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6530,7 +6606,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6579,22 +6655,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6632,7 +6708,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6646,7 +6722,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6695,22 +6771,22 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6743,12 +6819,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6762,7 +6838,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6811,22 +6887,22 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6859,12 +6935,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6878,7 +6954,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6903,22 +6979,18 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>141.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6931,7 +7003,7 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -6941,7 +7013,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -6984,7 +7056,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6998,7 +7070,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7023,22 +7095,18 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>130.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7119,7 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -7061,7 +7129,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -7104,7 +7172,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7118,7 +7186,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7143,92 +7211,84 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>137.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>104分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7242,7 +7302,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7252,65 +7312,61 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -7348,7 +7404,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7362,7 +7418,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7398,77 +7454,73 @@
       <c r="AC58" s="2" t="inlineStr"/>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7482,7 +7534,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7492,17 +7544,17 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7517,74 +7569,70 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7592,7 +7640,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7606,7 +7654,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7616,17 +7664,17 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7641,40 +7689,40 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7707,12 +7755,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7726,7 +7774,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7751,88 +7799,88 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7846,7 +7894,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7856,17 +7904,17 @@
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7876,45 +7924,41 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7947,12 +7991,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7966,7 +8010,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7991,46 +8035,50 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB63" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8063,12 +8111,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8082,7 +8130,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8112,41 +8160,45 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8179,12 +8231,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8198,7 +8250,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8223,46 +8275,50 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB65" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8295,12 +8351,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8314,7 +8370,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8350,7 +8406,7 @@
       <c r="AC66" s="2" t="inlineStr"/>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -8363,7 +8419,7 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -8373,7 +8429,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -8383,40 +8439,44 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8430,7 +8490,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8440,33 +8500,37 @@
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8479,7 +8543,7 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -8489,7 +8553,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8527,12 +8591,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8546,7 +8610,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8571,7 +8635,7 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
@@ -8595,7 +8659,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -8605,7 +8669,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8615,40 +8679,44 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8662,7 +8730,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8672,33 +8740,37 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB69" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8783,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8721,7 +8793,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8731,40 +8803,44 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8778,7 +8854,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8788,33 +8864,37 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB70" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8827,22 +8907,22 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>07:47</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8875,12 +8955,12 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8894,7 +8974,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8919,7 +8999,7 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
@@ -8943,60 +9023,64 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9010,7 +9094,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9020,33 +9104,37 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -9059,60 +9147,64 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>08:04</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>113分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9126,7 +9218,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9136,17 +9228,17 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9161,12 +9253,12 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9179,22 +9271,22 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -9232,7 +9324,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9246,7 +9338,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9271,7 +9363,7 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
@@ -9295,7 +9387,7 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -9305,7 +9397,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9315,40 +9407,44 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9362,7 +9458,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9372,17 +9468,17 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9397,12 +9493,12 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9511,7 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -9425,7 +9521,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9435,40 +9531,44 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9482,7 +9582,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9492,17 +9592,17 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9512,13 +9612,17 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC76" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9531,22 +9635,22 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -9579,12 +9683,12 @@
       <c r="N77" s="2" t="inlineStr"/>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9598,7 +9702,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9623,7 +9727,7 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
@@ -9647,7 +9751,7 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -9657,7 +9761,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -9695,12 +9799,12 @@
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9714,7 +9818,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9744,17 +9848,13 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC78" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr"/>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9767,7 +9867,7 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -9777,7 +9877,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -9787,40 +9887,44 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9834,7 +9938,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9844,17 +9948,17 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9869,12 +9973,12 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9887,7 +9991,7 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A57902D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -9897,7 +10001,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -9935,12 +10039,12 @@
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9954,7 +10058,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -9979,7 +10083,7 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
@@ -10003,22 +10107,22 @@
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -10051,12 +10155,12 @@
       <c r="N81" s="2" t="inlineStr"/>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10070,7 +10174,7 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
@@ -10105,6 +10209,2010 @@
       </c>
       <c r="AC81" s="2" t="inlineStr"/>
       <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr"/>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr"/>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr"/>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr"/>
+      <c r="AD97" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr"/>
+      <c r="AD98" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-20-operations.xlsx
+++ b/data/export/2026-10-20-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD98"/>
+  <dimension ref="A1:AD103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -848,17 +848,17 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,22 +1091,22 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2255,32 +2255,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -2288,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2312,33 +2316,37 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2371,32 +2379,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2404,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2428,17 +2440,17 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2448,17 +2460,17 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2491,32 +2503,36 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2524,7 +2540,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2548,17 +2564,17 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2568,17 +2584,17 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2611,32 +2627,36 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2644,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2668,37 +2688,37 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2784,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2818,7 +2838,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3020,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3120,7 +3140,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3174,7 +3194,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3260,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3294,7 +3314,7 @@
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3380,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3414,7 +3434,7 @@
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3500,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3600,7 +3620,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3720,7 +3740,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3774,7 +3794,7 @@
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3860,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3894,7 +3914,7 @@
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3907,22 +3927,22 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A67983D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3955,12 +3975,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3999,7 +4019,7 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -4009,40 +4029,40 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -4075,12 +4095,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4094,7 +4114,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4119,88 +4139,88 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4214,7 +4234,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4224,37 +4244,37 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4267,56 +4287,52 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:26</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4324,7 +4340,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4338,7 +4354,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4348,17 +4364,17 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4368,17 +4384,13 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr">
-        <is>
-          <t>126.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4391,24 +4403,24 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>06:31</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4421,24 +4433,24 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>152分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -4448,7 +4460,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4462,7 +4474,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4497,12 +4509,12 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4527,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4525,7 +4537,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4535,32 +4547,36 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq56，推进28站，达到≥2站确认条件</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4568,7 +4584,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4576,29 +4592,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>丁香路锦绣路</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>07:41</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>07:50</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 12分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4608,17 +4608,17 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4628,13 +4628,17 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4647,24 +4651,24 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>06:41</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4677,7 +4681,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4689,22 +4693,22 @@
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4718,7 +4722,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4771,56 +4775,52 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq56，推进28站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4828,7 +4828,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4836,13 +4836,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr"/>
-      <c r="U36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 12分钟参与校验</t>
+        </is>
+      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4852,17 +4868,17 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4872,17 +4888,13 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr">
-        <is>
-          <t>146.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4895,7 +4907,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4905,7 +4917,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4925,34 +4937,34 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>159分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4966,7 +4978,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -5001,12 +5013,12 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5031,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -5029,7 +5041,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -5039,40 +5051,44 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5086,7 +5102,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5096,33 +5112,37 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5155,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5145,7 +5165,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5155,40 +5175,44 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5202,7 +5226,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5212,17 +5236,17 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5232,13 +5256,17 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5251,7 +5279,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5261,7 +5289,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5299,12 +5327,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5318,7 +5346,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5343,7 +5371,7 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
@@ -5367,32 +5395,32 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq41推进至seq44，推进3站，达到≥2站确认条件</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -5415,12 +5443,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5428,25 +5456,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>物理seq23（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>08:29</t>
-        </is>
-      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
       <c r="T41" s="2" t="inlineStr"/>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>区间折返已由主分类器确认；折返点按重建物理位置seq23映射；现有采样不足以把折返发车时间控制在±10分钟</t>
-        </is>
-      </c>
+      <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5471,7 +5487,7 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
@@ -5495,22 +5511,22 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5543,12 +5559,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5562,7 +5578,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5611,7 +5627,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5621,7 +5637,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5631,12 +5647,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq41推进至seq50，推进9站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5659,12 +5675,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5672,13 +5688,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr"/>
-      <c r="S43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
       <c r="T43" s="2" t="inlineStr"/>
-      <c r="U43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq23映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5727,22 +5755,22 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>07:24</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5775,12 +5803,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5794,7 +5822,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5843,22 +5871,22 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5891,12 +5919,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5910,7 +5938,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5959,7 +5987,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5969,7 +5997,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5979,12 +6007,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq39推进至seq47，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -6007,12 +6035,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6020,13 +6048,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R46" s="2" t="inlineStr"/>
-      <c r="S46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
       <c r="T46" s="2" t="inlineStr"/>
-      <c r="U46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq23映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -6075,7 +6115,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -6085,7 +6125,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -6123,12 +6163,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6142,7 +6182,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6191,7 +6231,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6201,7 +6241,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6239,12 +6279,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6258,7 +6298,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6307,7 +6347,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6317,7 +6357,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6355,12 +6395,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6374,7 +6414,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6423,7 +6463,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6433,7 +6473,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6471,12 +6511,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6490,7 +6530,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6539,7 +6579,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6549,7 +6589,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6587,12 +6627,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6606,7 +6646,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6655,7 +6695,7 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6665,7 +6705,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -6703,12 +6743,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6722,7 +6762,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6771,7 +6811,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6781,7 +6821,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6819,12 +6859,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6838,7 +6878,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6887,7 +6927,7 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -6897,7 +6937,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -6935,12 +6975,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6954,7 +6994,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -7003,22 +7043,22 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -7056,7 +7096,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7070,7 +7110,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7119,22 +7159,22 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -7167,12 +7207,12 @@
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7186,7 +7226,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7235,7 +7275,7 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -7245,7 +7285,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -7283,12 +7323,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7302,7 +7342,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7351,7 +7391,7 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -7361,7 +7401,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7404,7 +7444,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7418,7 +7458,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7443,7 +7483,7 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
@@ -7467,7 +7507,7 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -7477,7 +7517,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -7515,12 +7555,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7534,7 +7574,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7559,22 +7599,18 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr">
-        <is>
-          <t>130.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -7587,7 +7623,7 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -7597,7 +7633,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -7640,7 +7676,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7654,7 +7690,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7684,17 +7720,13 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr">
-        <is>
-          <t>152.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -7707,7 +7739,7 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -7717,7 +7749,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -7760,7 +7792,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7774,7 +7806,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7809,12 +7841,12 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -7827,7 +7859,7 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -7837,7 +7869,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -7880,7 +7912,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7894,7 +7926,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7924,13 +7956,17 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -7943,7 +7979,7 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -7953,7 +7989,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -7991,12 +8027,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8010,7 +8046,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -8045,12 +8081,12 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -8063,7 +8099,7 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -8073,7 +8109,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -8116,7 +8152,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8130,7 +8166,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8160,17 +8196,13 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr">
-        <is>
-          <t>146.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -8183,7 +8215,7 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -8193,7 +8225,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -8231,12 +8263,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8250,7 +8282,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8285,12 +8317,12 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -8303,22 +8335,22 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8351,12 +8383,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8370,7 +8402,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8400,83 +8432,83 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>104分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8490,7 +8522,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8500,17 +8532,17 @@
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8525,40 +8557,40 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8591,12 +8623,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8610,7 +8642,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8646,77 +8678,73 @@
       <c r="AC68" s="2" t="inlineStr"/>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8730,7 +8758,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8740,17 +8768,17 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8760,17 +8788,13 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -8783,7 +8807,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8793,7 +8817,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8813,24 +8837,24 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -8840,7 +8864,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8854,7 +8878,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8884,17 +8908,17 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8907,7 +8931,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -8917,7 +8941,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8955,12 +8979,12 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8974,7 +8998,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8999,7 +9023,7 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
@@ -9023,7 +9047,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -9033,7 +9057,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -9053,24 +9077,24 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
@@ -9080,7 +9104,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9094,7 +9118,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9129,12 +9153,12 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9147,7 +9171,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -9157,7 +9181,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9177,34 +9201,34 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>113分钟</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9218,7 +9242,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9253,12 +9277,12 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9271,22 +9295,22 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -9319,12 +9343,12 @@
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9338,7 +9362,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9387,24 +9411,24 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>07:10</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9417,34 +9441,34 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>104分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9458,7 +9482,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9493,12 +9517,12 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -9511,24 +9535,24 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9541,12 +9565,12 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>113分钟</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
@@ -9563,12 +9587,12 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9582,7 +9606,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9617,12 +9641,12 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>113.0</t>
         </is>
       </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9635,22 +9659,22 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>07:20</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -9683,12 +9707,12 @@
       <c r="N77" s="2" t="inlineStr"/>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9702,7 +9726,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9751,7 +9775,7 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -9761,7 +9785,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -9771,40 +9795,44 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9818,7 +9846,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9828,17 +9856,17 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9848,13 +9876,17 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC78" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9867,7 +9899,7 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -9877,7 +9909,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -9897,34 +9929,34 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9938,7 +9970,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9973,12 +10005,12 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9991,7 +10023,7 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -10001,7 +10033,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -10039,12 +10071,12 @@
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10058,7 +10090,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -10083,7 +10115,7 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
@@ -10107,22 +10139,22 @@
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>07:47</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -10155,12 +10187,12 @@
       <c r="N81" s="2" t="inlineStr"/>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10174,7 +10206,7 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
@@ -10223,52 +10255,56 @@
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr"/>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10276,7 +10312,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10290,7 +10326,7 @@
       <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
@@ -10300,33 +10336,37 @@
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB82" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -10339,60 +10379,64 @@
       <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A57902D</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>08:04</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr"/>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N83" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10406,7 +10450,7 @@
       <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
@@ -10416,22 +10460,22 @@
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
@@ -10441,12 +10485,12 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -10459,22 +10503,22 @@
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -10507,12 +10551,12 @@
       <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10526,7 +10570,7 @@
       <c r="U84" s="2" t="inlineStr"/>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
@@ -10551,7 +10595,7 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
@@ -10575,7 +10619,7 @@
       <c r="B85" s="2" t="inlineStr"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -10585,7 +10629,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -10623,12 +10667,12 @@
       <c r="N85" s="2" t="inlineStr"/>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10642,7 +10686,7 @@
       <c r="U85" s="2" t="inlineStr"/>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
@@ -10667,22 +10711,18 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC85" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr"/>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10735,7 @@
       <c r="B86" s="2" t="inlineStr"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -10705,7 +10745,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -10715,32 +10755,36 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr"/>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10748,7 +10792,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10762,7 +10806,7 @@
       <c r="U86" s="2" t="inlineStr"/>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
@@ -10772,17 +10816,17 @@
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
@@ -10792,13 +10836,17 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC86" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10811,22 +10859,22 @@
       <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -10859,12 +10907,12 @@
       <c r="N87" s="2" t="inlineStr"/>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10878,7 +10926,7 @@
       <c r="U87" s="2" t="inlineStr"/>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
@@ -10903,7 +10951,7 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
@@ -10927,7 +10975,7 @@
       <c r="B88" s="2" t="inlineStr"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -10937,7 +10985,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -10980,7 +11028,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10994,7 +11042,7 @@
       <c r="U88" s="2" t="inlineStr"/>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
@@ -11029,12 +11077,12 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -11047,7 +11095,7 @@
       <c r="B89" s="2" t="inlineStr"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -11057,7 +11105,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -11100,7 +11148,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11114,7 +11162,7 @@
       <c r="U89" s="2" t="inlineStr"/>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
@@ -11139,22 +11187,18 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC89" s="2" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr"/>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -11167,7 +11211,7 @@
       <c r="B90" s="2" t="inlineStr"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -11177,7 +11221,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -11215,12 +11259,12 @@
       <c r="N90" s="2" t="inlineStr"/>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11234,7 +11278,7 @@
       <c r="U90" s="2" t="inlineStr"/>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
@@ -11259,7 +11303,7 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
@@ -11283,7 +11327,7 @@
       <c r="B91" s="2" t="inlineStr"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -11293,7 +11337,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -11336,7 +11380,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11350,7 +11394,7 @@
       <c r="U91" s="2" t="inlineStr"/>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
@@ -11380,13 +11424,17 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC91" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -11399,7 +11447,7 @@
       <c r="B92" s="2" t="inlineStr"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -11409,7 +11457,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -11447,12 +11495,12 @@
       <c r="N92" s="2" t="inlineStr"/>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11466,7 +11514,7 @@
       <c r="U92" s="2" t="inlineStr"/>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
@@ -11501,12 +11549,12 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -11519,22 +11567,22 @@
       <c r="B93" s="2" t="inlineStr"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -11567,12 +11615,12 @@
       <c r="N93" s="2" t="inlineStr"/>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11586,7 +11634,7 @@
       <c r="U93" s="2" t="inlineStr"/>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
@@ -11616,17 +11664,13 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC93" s="2" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr"/>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -11639,22 +11683,22 @@
       <c r="B94" s="2" t="inlineStr"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -11687,12 +11731,12 @@
       <c r="N94" s="2" t="inlineStr"/>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -11706,7 +11750,7 @@
       <c r="U94" s="2" t="inlineStr"/>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
@@ -11736,17 +11780,13 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC94" s="2" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr"/>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -11759,7 +11799,7 @@
       <c r="B95" s="2" t="inlineStr"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -11769,7 +11809,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -11807,12 +11847,12 @@
       <c r="N95" s="2" t="inlineStr"/>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -11826,7 +11866,7 @@
       <c r="U95" s="2" t="inlineStr"/>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
@@ -11856,13 +11896,17 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC95" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -11875,7 +11919,7 @@
       <c r="B96" s="2" t="inlineStr"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -11885,7 +11929,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -11923,12 +11967,12 @@
       <c r="N96" s="2" t="inlineStr"/>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11942,7 +11986,7 @@
       <c r="U96" s="2" t="inlineStr"/>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
@@ -11977,12 +12021,12 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -11995,7 +12039,7 @@
       <c r="B97" s="2" t="inlineStr"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -12005,7 +12049,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -12043,12 +12087,12 @@
       <c r="N97" s="2" t="inlineStr"/>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12062,7 +12106,7 @@
       <c r="U97" s="2" t="inlineStr"/>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
@@ -12092,13 +12136,17 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC97" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -12111,22 +12159,22 @@
       <c r="B98" s="2" t="inlineStr"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -12159,12 +12207,12 @@
       <c r="N98" s="2" t="inlineStr"/>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12178,7 +12226,7 @@
       <c r="U98" s="2" t="inlineStr"/>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
@@ -12213,6 +12261,590 @@
       </c>
       <c r="AC98" s="2" t="inlineStr"/>
       <c r="AD98" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD99" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr"/>
+      <c r="AD100" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr"/>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr"/>
+      <c r="AD101" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr"/>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr"/>
+      <c r="AD102" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr"/>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr"/>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr"/>
+      <c r="AD103" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-20-operations.xlsx
+++ b/data/export/2026-10-20-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,12 +724,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1840,17 +1840,17 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2088,12 +2088,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3444,17 +3444,17 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5056,17 +5056,17 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6420,12 +6420,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7284,17 +7284,17 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7364,7 +7364,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8152,12 +8152,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8276,17 +8276,17 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -8480,7 +8480,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8524,12 +8524,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9268,12 +9268,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9516,12 +9516,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
@@ -10204,7 +10204,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10248,12 +10248,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10372,17 +10372,17 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD82" s="2" t="inlineStr">
@@ -10944,7 +10944,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10988,12 +10988,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AD85" s="2" t="inlineStr">
@@ -11118,7 +11118,7 @@
       </c>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -11312,7 +11312,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11356,12 +11356,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
@@ -11523,32 +11523,36 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr"/>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N90" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11556,7 +11560,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11580,17 +11584,17 @@
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA90" s="2" t="inlineStr">
@@ -11600,17 +11604,17 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -11653,24 +11657,24 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
@@ -11680,7 +11684,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11729,7 +11733,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
@@ -11767,32 +11771,36 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N92" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11800,7 +11808,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11824,17 +11832,17 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
@@ -11844,12 +11852,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
@@ -11887,32 +11895,36 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -11920,7 +11932,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11944,17 +11956,17 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11964,12 +11976,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
@@ -12007,32 +12019,36 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:27</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -12040,7 +12056,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12064,17 +12080,17 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -12084,12 +12100,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
@@ -12127,32 +12143,36 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -12160,7 +12180,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12184,17 +12204,17 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA95" s="2" t="inlineStr">
@@ -12204,12 +12224,12 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
@@ -12280,7 +12300,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12329,7 +12349,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
@@ -12400,7 +12420,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12444,12 +12464,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
@@ -12574,7 +12594,7 @@
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -12644,7 +12664,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12688,17 +12708,17 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -12946,7 +12966,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -13148,7 +13168,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13202,7 +13222,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -13326,7 +13346,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -13450,7 +13470,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -13574,7 +13594,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -13644,7 +13664,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13698,7 +13718,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -13768,7 +13788,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13812,17 +13832,17 @@
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>146.3</t>
         </is>
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -13954,7 +13974,7 @@
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -14144,7 +14164,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14188,12 +14208,12 @@
       </c>
       <c r="AB111" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC111" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AD111" s="2" t="inlineStr">
@@ -14264,7 +14284,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14330,7 +14350,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -14400,7 +14420,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14454,7 +14474,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -14698,7 +14718,7 @@
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -14768,7 +14788,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14822,7 +14842,7 @@
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -14892,7 +14912,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -15012,7 +15032,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15066,7 +15086,7 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -15190,7 +15210,7 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -15260,7 +15280,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15304,17 +15324,17 @@
       </c>
       <c r="AB120" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC120" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -15438,7 +15458,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>25/31</t>
+          <t>28/31</t>
         </is>
       </c>
     </row>
@@ -15508,7 +15528,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15562,7 +15582,7 @@
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -15632,7 +15652,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15676,17 +15696,17 @@
       </c>
       <c r="AB123" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC123" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -15872,7 +15892,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -15926,7 +15946,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -16046,7 +16066,7 @@
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -16112,7 +16132,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -16156,17 +16176,17 @@
       </c>
       <c r="AB127" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC127" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -16290,7 +16310,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -16616,7 +16636,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -16670,7 +16690,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -16794,7 +16814,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -16918,7 +16938,7 @@
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -17042,7 +17062,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -17112,7 +17132,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17166,7 +17186,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -17236,7 +17256,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -17280,17 +17300,17 @@
       </c>
       <c r="AB136" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC136" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>146.3</t>
         </is>
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -17360,7 +17380,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -17404,12 +17424,12 @@
       </c>
       <c r="AB137" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC137" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AD137" s="2" t="inlineStr">
@@ -17728,7 +17748,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17782,7 +17802,7 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -17852,7 +17872,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -17906,7 +17926,7 @@
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -18030,7 +18050,7 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -18100,7 +18120,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18224,7 +18244,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18278,7 +18298,7 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -18402,7 +18422,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -18472,7 +18492,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -18526,7 +18546,7 @@
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -18720,7 +18740,7 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
@@ -18774,7 +18794,7 @@
       </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -18898,7 +18918,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -19146,7 +19166,7 @@
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -19270,7 +19290,7 @@
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -19336,7 +19356,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -19522,7 +19542,7 @@
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -19716,7 +19736,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19770,7 +19790,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -19894,7 +19914,7 @@
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -20142,7 +20162,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -20212,7 +20232,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20266,7 +20286,7 @@
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -20514,7 +20534,7 @@
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -20638,7 +20658,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -20762,7 +20782,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -20886,7 +20906,7 @@
       </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -20952,7 +20972,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q166" s="2" t="inlineStr">
@@ -20996,17 +21016,17 @@
       </c>
       <c r="AB166" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC166" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>146.3</t>
         </is>
       </c>
       <c r="AD166" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -21130,7 +21150,7 @@
       </c>
       <c r="AD167" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -21452,7 +21472,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21568,7 +21588,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21612,17 +21632,17 @@
       </c>
       <c r="AB171" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC171" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -21692,7 +21712,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21736,17 +21756,17 @@
       </c>
       <c r="AB172" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC172" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -21816,7 +21836,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21860,12 +21880,12 @@
       </c>
       <c r="AB173" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC173" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AD173" s="2" t="inlineStr">
@@ -21940,7 +21960,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -21994,7 +22014,7 @@
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -22060,7 +22080,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22114,7 +22134,7 @@
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -22184,7 +22204,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22238,7 +22258,7 @@
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -22308,7 +22328,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22352,17 +22372,17 @@
       </c>
       <c r="AB177" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC177" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -22432,7 +22452,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22486,7 +22506,7 @@
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -22556,7 +22576,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22610,7 +22630,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -22734,7 +22754,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -22804,7 +22824,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -22858,7 +22878,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -22928,7 +22948,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -22982,7 +23002,7 @@
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -23230,7 +23250,7 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -23354,7 +23374,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -23478,7 +23498,7 @@
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -23602,7 +23622,7 @@
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -23722,7 +23742,7 @@
       </c>
       <c r="AD188" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -23792,7 +23812,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -23879,32 +23899,36 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr"/>
       <c r="M190" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N190" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -23912,7 +23936,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -23936,17 +23960,17 @@
       </c>
       <c r="X190" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z190" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA190" s="2" t="inlineStr">
@@ -23956,17 +23980,17 @@
       </c>
       <c r="AB190" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC190" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>27/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -23999,32 +24023,36 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr"/>
       <c r="M191" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N191" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
           <t>17:51</t>
@@ -24032,7 +24060,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -24056,17 +24084,17 @@
       </c>
       <c r="X191" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z191" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA191" s="2" t="inlineStr">
@@ -24076,13 +24104,17 @@
       </c>
       <c r="AB191" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC191" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC191" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>—/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -24115,32 +24147,36 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr"/>
       <c r="M192" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N192" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -24148,7 +24184,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24172,17 +24208,17 @@
       </c>
       <c r="X192" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z192" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA192" s="2" t="inlineStr">
@@ -24192,17 +24228,17 @@
       </c>
       <c r="AB192" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC192" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -24235,32 +24271,36 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr"/>
       <c r="M193" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N193" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N193" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -24268,7 +24308,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24292,17 +24332,17 @@
       </c>
       <c r="X193" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z193" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA193" s="2" t="inlineStr">
@@ -24312,17 +24352,17 @@
       </c>
       <c r="AB193" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC193" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>146.3</t>
         </is>
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>26/31</t>
+          <t>27/31</t>
         </is>
       </c>
     </row>
@@ -24355,12 +24395,12 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
@@ -24388,7 +24428,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24396,10 +24436,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R194" s="2" t="inlineStr"/>
-      <c r="S194" s="2" t="inlineStr"/>
-      <c r="T194" s="2" t="inlineStr"/>
-      <c r="U194" s="2" t="inlineStr"/>
+      <c r="R194" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S194" s="2" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
+      <c r="T194" s="2" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="U194" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V194" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -24442,7 +24498,7 @@
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -24475,32 +24531,36 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr"/>
       <c r="M195" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N195" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N195" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O195" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -24508,7 +24568,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24532,17 +24592,17 @@
       </c>
       <c r="X195" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z195" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA195" s="2" t="inlineStr">
@@ -24552,17 +24612,17 @@
       </c>
       <c r="AB195" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC195" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -24595,32 +24655,36 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:33</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K196" s="2" t="inlineStr"/>
       <c r="L196" s="2" t="inlineStr"/>
       <c r="M196" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N196" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N196" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -24628,7 +24692,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24652,17 +24716,17 @@
       </c>
       <c r="X196" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z196" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA196" s="2" t="inlineStr">
@@ -24672,12 +24736,12 @@
       </c>
       <c r="AB196" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC196" s="2" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AD196" s="2" t="inlineStr">
@@ -24748,7 +24812,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24802,7 +24866,7 @@
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -24835,12 +24899,12 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq28推进至seq57，推进29站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
@@ -24868,7 +24932,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24876,10 +24940,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R198" s="2" t="inlineStr"/>
-      <c r="S198" s="2" t="inlineStr"/>
-      <c r="T198" s="2" t="inlineStr"/>
-      <c r="U198" s="2" t="inlineStr"/>
+      <c r="R198" s="2" t="inlineStr">
+        <is>
+          <t>物理seq30（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S198" s="2" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="T198" s="2" t="inlineStr">
+        <is>
+          <t>20:28</t>
+        </is>
+      </c>
+      <c r="U198" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±3分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V198" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -24922,7 +25002,7 @@
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -24988,7 +25068,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25042,7 +25122,7 @@
       </c>
       <c r="AD199" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -25108,7 +25188,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25162,7 +25242,7 @@
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -25228,7 +25308,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25282,7 +25362,7 @@
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -25348,7 +25428,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25402,7 +25482,7 @@
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -25468,7 +25548,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25522,7 +25602,7 @@
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -25588,7 +25668,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25712,7 +25792,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25756,17 +25836,17 @@
       </c>
       <c r="AB205" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC205" s="2" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -25886,7 +25966,7 @@
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -26200,7 +26280,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q209" s="2" t="inlineStr">
@@ -26244,12 +26324,12 @@
       </c>
       <c r="AB209" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC209" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD209" s="2" t="inlineStr">
@@ -26324,7 +26404,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q210" s="2" t="inlineStr">
@@ -26373,12 +26453,12 @@
       </c>
       <c r="AC210" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -26502,7 +26582,7 @@
       </c>
       <c r="AD211" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -26622,7 +26702,7 @@
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -26692,7 +26772,7 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q213" s="2" t="inlineStr">
@@ -26746,7 +26826,7 @@
       </c>
       <c r="AD213" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -26816,7 +26896,7 @@
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q214" s="2" t="inlineStr">
@@ -26860,17 +26940,17 @@
       </c>
       <c r="AB214" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC214" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AD214" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -27668,7 +27748,7 @@
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q221" s="2" t="inlineStr">
@@ -27712,17 +27792,17 @@
       </c>
       <c r="AB221" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC221" s="2" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -27792,7 +27872,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -27836,17 +27916,17 @@
       </c>
       <c r="AB222" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC222" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -28094,7 +28174,7 @@
       </c>
       <c r="AD224" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -28288,7 +28368,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q226" s="2" t="inlineStr">
@@ -28337,12 +28417,12 @@
       </c>
       <c r="AC226" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -28528,7 +28608,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
@@ -28572,12 +28652,12 @@
       </c>
       <c r="AB228" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC228" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD228" s="2" t="inlineStr">
@@ -28706,7 +28786,7 @@
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -28830,7 +28910,7 @@
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -28900,7 +28980,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q231" s="2" t="inlineStr">
@@ -28944,17 +29024,17 @@
       </c>
       <c r="AB231" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC231" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AD231" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -29024,7 +29104,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q232" s="2" t="inlineStr">
@@ -29078,7 +29158,7 @@
       </c>
       <c r="AD232" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -29640,7 +29720,7 @@
       </c>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q237" s="2" t="inlineStr">
@@ -29684,17 +29764,17 @@
       </c>
       <c r="AB237" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC237" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD237" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -29818,7 +29898,7 @@
       </c>
       <c r="AD238" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -30132,7 +30212,7 @@
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q241" s="2" t="inlineStr">
@@ -30193,12 +30273,12 @@
       </c>
       <c r="AC241" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AD241" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -30322,7 +30402,7 @@
       </c>
       <c r="AD242" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -30446,7 +30526,7 @@
       </c>
       <c r="AD243" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -30512,7 +30592,7 @@
       </c>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q244" s="2" t="inlineStr">
@@ -30568,17 +30648,17 @@
       </c>
       <c r="AB244" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC244" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AD244" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -31198,7 +31278,7 @@
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -31570,7 +31650,7 @@
       </c>
       <c r="AD252" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -31694,7 +31774,7 @@
       </c>
       <c r="AD253" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -32310,7 +32390,7 @@
       </c>
       <c r="AD258" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -32628,7 +32708,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q261" s="2" t="inlineStr">
@@ -32672,17 +32752,17 @@
       </c>
       <c r="AB261" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC261" s="2" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -32806,7 +32886,7 @@
       </c>
       <c r="AD262" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -32930,7 +33010,7 @@
       </c>
       <c r="AD263" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -33244,7 +33324,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q266" s="2" t="inlineStr">
@@ -33288,12 +33368,12 @@
       </c>
       <c r="AB266" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC266" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD266" s="2" t="inlineStr">
@@ -33492,7 +33572,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -33546,7 +33626,7 @@
       </c>
       <c r="AD268" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -33984,7 +34064,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -34033,12 +34113,12 @@
       </c>
       <c r="AC272" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AD272" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -34108,7 +34188,7 @@
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q273" s="2" t="inlineStr">
@@ -34152,17 +34232,17 @@
       </c>
       <c r="AB273" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC273" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD273" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -34286,7 +34366,7 @@
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -34480,7 +34560,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q276" s="2" t="inlineStr">
@@ -34524,17 +34604,17 @@
       </c>
       <c r="AB276" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC276" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -34782,7 +34862,7 @@
       </c>
       <c r="AD278" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -34852,7 +34932,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q279" s="2" t="inlineStr">
@@ -34896,17 +34976,17 @@
       </c>
       <c r="AB279" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC279" s="2" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AD279" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -35030,7 +35110,7 @@
       </c>
       <c r="AD280" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -35588,7 +35668,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35632,12 +35712,12 @@
       </c>
       <c r="AB285" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC285" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD285" s="2" t="inlineStr">
@@ -35712,7 +35792,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35766,7 +35846,7 @@
       </c>
       <c r="AD286" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -36084,7 +36164,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -36128,17 +36208,17 @@
       </c>
       <c r="AB289" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC289" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD289" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -36208,7 +36288,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q290" s="2" t="inlineStr">
@@ -36257,12 +36337,12 @@
       </c>
       <c r="AC290" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AD290" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -36386,7 +36466,7 @@
       </c>
       <c r="AD291" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -36576,7 +36656,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q293" s="2" t="inlineStr">
@@ -36620,17 +36700,17 @@
       </c>
       <c r="AB293" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC293" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AD293" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -36754,7 +36834,7 @@
       </c>
       <c r="AD294" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -37068,7 +37148,7 @@
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q297" s="2" t="inlineStr">
@@ -37112,17 +37192,17 @@
       </c>
       <c r="AB297" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC297" s="2" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AD297" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -37564,7 +37644,7 @@
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q301" s="2" t="inlineStr">
@@ -37608,12 +37688,12 @@
       </c>
       <c r="AB301" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC301" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD301" s="2" t="inlineStr">
@@ -37661,12 +37741,12 @@
       </c>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="J302" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K302" s="2" t="inlineStr"/>
@@ -37688,7 +37768,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37737,12 +37817,12 @@
       </c>
       <c r="AC302" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AD302" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -37808,7 +37888,7 @@
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q303" s="2" t="inlineStr">
@@ -37862,7 +37942,7 @@
       </c>
       <c r="AD303" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -37895,32 +37975,36 @@
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="J304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K304" s="2" t="inlineStr"/>
       <c r="L304" s="2" t="inlineStr"/>
       <c r="M304" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N304" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N304" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O304" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -37928,7 +38012,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -37952,17 +38036,17 @@
       </c>
       <c r="X304" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z304" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA304" s="2" t="inlineStr">
@@ -37972,17 +38056,17 @@
       </c>
       <c r="AB304" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC304" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AD304" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -38015,32 +38099,36 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="J305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K305" s="2" t="inlineStr"/>
       <c r="L305" s="2" t="inlineStr"/>
       <c r="M305" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N305" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N305" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O305" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -38048,7 +38136,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q305" s="2" t="inlineStr">
@@ -38072,17 +38160,17 @@
       </c>
       <c r="X305" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z305" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA305" s="2" t="inlineStr">
@@ -38092,17 +38180,17 @@
       </c>
       <c r="AB305" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC305" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD305" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -38135,32 +38223,36 @@
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:39</t>
         </is>
       </c>
       <c r="J306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K306" s="2" t="inlineStr"/>
       <c r="L306" s="2" t="inlineStr"/>
       <c r="M306" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N306" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N306" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O306" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -38168,7 +38260,7 @@
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q306" s="2" t="inlineStr">
@@ -38192,17 +38284,17 @@
       </c>
       <c r="X306" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z306" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA306" s="2" t="inlineStr">
@@ -38212,17 +38304,17 @@
       </c>
       <c r="AB306" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC306" s="2" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AD306" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -38255,32 +38347,36 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I307" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="J307" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K307" s="2" t="inlineStr"/>
       <c r="L307" s="2" t="inlineStr"/>
       <c r="M307" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N307" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N307" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O307" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -38288,7 +38384,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q307" s="2" t="inlineStr">
@@ -38312,17 +38408,17 @@
       </c>
       <c r="X307" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y307" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z307" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA307" s="2" t="inlineStr">
@@ -38332,12 +38428,12 @@
       </c>
       <c r="AB307" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC307" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD307" s="2" t="inlineStr">
@@ -38408,7 +38504,7 @@
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q308" s="2" t="inlineStr">
@@ -38462,7 +38558,7 @@
       </c>
       <c r="AD308" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -38528,7 +38624,7 @@
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q309" s="2" t="inlineStr">
@@ -38572,17 +38668,17 @@
       </c>
       <c r="AB309" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC309" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD309" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
